--- a/chapters/07/core/AIHE-B04/supp/AIHE-EX18/xlsx/AIHE-EX18_workbook.xlsx
+++ b/chapters/07/core/AIHE-B04/supp/AIHE-EX18/xlsx/AIHE-EX18_workbook.xlsx
@@ -87,7 +87,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
